--- a/Template_llenado.xlsx
+++ b/Template_llenado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programacion\Proyecto-Analitica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BFF74F220C45C5CF2D0584A6F8021E8047ED04A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4659C1-6591-4223-B80C-AF814AF7F553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,28 +73,28 @@
     <t>bases de datos donde escribe:</t>
   </si>
   <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>Escribe datos en Bases de datos</t>
+  </si>
+  <si>
+    <t>bases de datos consultadas:</t>
+  </si>
+  <si>
+    <t>Lee datos de bases de datos</t>
+  </si>
+  <si>
+    <t>Servidor donde está desplegada la solución</t>
+  </si>
+  <si>
+    <t>localhost / Windows 11</t>
+  </si>
+  <si>
+    <t>En desarrollo</t>
+  </si>
+  <si>
     <t>peliculas_db</t>
-  </si>
-  <si>
-    <t>root</t>
-  </si>
-  <si>
-    <t>Escribe datos en Bases de datos</t>
-  </si>
-  <si>
-    <t>bases de datos consultadas:</t>
-  </si>
-  <si>
-    <t>Lee datos de bases de datos</t>
-  </si>
-  <si>
-    <t>Servidor donde está desplegada la solución</t>
-  </si>
-  <si>
-    <t>localhost / Windows 11</t>
-  </si>
-  <si>
-    <t>En desarrollo</t>
   </si>
 </sst>
 </file>
@@ -434,6 +434,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -447,11 +452,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -783,13 +783,13 @@
       <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -831,13 +831,13 @@
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="33" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="31" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="12"/>
@@ -890,16 +890,16 @@
         <v>16</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>17</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>18</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -927,19 +927,19 @@
       <c r="B16" s="22"/>
       <c r="C16" s="23"/>
       <c r="D16" s="25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>17</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>18</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -981,17 +981,17 @@
     </row>
     <row r="22" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="D22" s="30"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="27"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="2"/>

--- a/Template_llenado.xlsx
+++ b/Template_llenado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programacion\Proyecto-Analitica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689B5C74-F24D-40F4-B7B0-5C61BE6ADCEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDF642D-5193-4913-9555-E9854F63128D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t xml:space="preserve">Nombre de los Integrantes </t>
   </si>
   <si>
-    <t>JHOVER INCHAPIE SANTOS HERNANDEZ -- MARCOS DANIEL ARGEL AVILA -- JHON KENNEDY USUGA</t>
-  </si>
-  <si>
     <t>Tiene repositorio GIT (Si/No)</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
   </si>
   <si>
     <t>En desarrollo</t>
+  </si>
+  <si>
+    <t>JHOVER INCAPIE HERNANDEZ -- MARCOS DANIEL ARGEL AVILA -- JHON KENNEDY USUGA</t>
   </si>
 </sst>
 </file>
@@ -396,62 +396,62 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -770,234 +770,243 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="25"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="C4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="D7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="14"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="14"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="15"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="2:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="D12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="E12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="21"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="21"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="14"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="14"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="15"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="17" t="s">
+      <c r="E16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="18"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="14"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="16"/>
       <c r="G18" s="4"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="19"/>
+      <c r="F19" s="17"/>
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="9"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="23" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="2"/>
+      <c r="C23" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="30"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="E8:G8"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="C6:G6"/>
@@ -1014,15 +1023,6 @@
     <mergeCell ref="D16:D19"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="E8:G8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
